--- a/_OUTPUT--Coordinator.xlsx
+++ b/_OUTPUT--Coordinator.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Coordinator" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -419,50 +419,8 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN1"/>
+  <dimension ref="A1:AP1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="12.35" customWidth="1" min="1" max="1"/>
-    <col width="18.1" customWidth="1" min="2" max="2"/>
-    <col width="16.95" customWidth="1" min="3" max="3"/>
-    <col width="10.05" customWidth="1" min="4" max="4"/>
-    <col width="13.5" customWidth="1" min="5" max="5"/>
-    <col width="16.95" customWidth="1" min="6" max="6"/>
-    <col width="10.05" customWidth="1" min="7" max="7"/>
-    <col width="11.2" customWidth="1" min="8" max="8"/>
-    <col width="39.95" customWidth="1" min="9" max="9"/>
-    <col width="16.95" customWidth="1" min="10" max="10"/>
-    <col width="12.35" customWidth="1" min="11" max="11"/>
-    <col width="27.3" customWidth="1" min="12" max="12"/>
-    <col width="12.35" customWidth="1" min="13" max="13"/>
-    <col width="33.05" customWidth="1" min="14" max="14"/>
-    <col width="12.35" customWidth="1" min="15" max="15"/>
-    <col width="34.2" customWidth="1" min="16" max="16"/>
-    <col width="12.35" customWidth="1" min="17" max="17"/>
-    <col width="26.15" customWidth="1" min="18" max="18"/>
-    <col width="12.35" customWidth="1" min="19" max="19"/>
-    <col width="31.9" customWidth="1" min="20" max="20"/>
-    <col width="12.35" customWidth="1" min="21" max="21"/>
-    <col width="36.5" customWidth="1" min="22" max="22"/>
-    <col width="12.35" customWidth="1" min="23" max="23"/>
-    <col width="28.45" customWidth="1" min="24" max="24"/>
-    <col width="12.35" customWidth="1" min="25" max="25"/>
-    <col width="29.6" customWidth="1" min="26" max="26"/>
-    <col width="14.65" customWidth="1" min="27" max="27"/>
-    <col width="31.9" customWidth="1" min="28" max="28"/>
-    <col width="14.65" customWidth="1" min="29" max="29"/>
-    <col width="13.5" customWidth="1" min="30" max="30"/>
-    <col width="31.9" customWidth="1" min="31" max="31"/>
-    <col width="31.9" customWidth="1" min="32" max="32"/>
-    <col width="31.9" customWidth="1" min="33" max="33"/>
-    <col width="12.35" customWidth="1" min="34" max="34"/>
-    <col width="13.5" customWidth="1" min="35" max="35"/>
-    <col width="10" customWidth="1" min="36" max="36"/>
-    <col width="10.05" customWidth="1" min="37" max="37"/>
-    <col width="10" customWidth="1" min="38" max="38"/>
-    <col width="10.05" customWidth="1" min="39" max="39"/>
-    <col width="11.2" customWidth="1" min="40" max="40"/>
-  </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
@@ -507,12 +465,12 @@
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>Gujarat/Gujarati (EXPLICIT - Y/N)</t>
+          <t>Gujarat/Gujarati</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>Auto_DQ (Y/N)</t>
+          <t>Auto_DQ</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
@@ -522,7 +480,7 @@
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>Dim1_Title_Score (0-3)</t>
+          <t>Dim1_Title_Score</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
@@ -532,7 +490,7 @@
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>Dim2_HighVolume_Score (0-3)</t>
+          <t>Dim2_HighVolume_Score</t>
         </is>
       </c>
       <c r="O1" s="1" t="inlineStr">
@@ -542,7 +500,7 @@
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
-          <t>Dim3_SalesHiring_Score (0-3)</t>
+          <t>Dim3_SaaS_Score</t>
         </is>
       </c>
       <c r="Q1" s="1" t="inlineStr">
@@ -552,7 +510,7 @@
       </c>
       <c r="R1" s="1" t="inlineStr">
         <is>
-          <t>Dim4_SaaS_Score (0-4)</t>
+          <t>Dim4_RecruitingOps_Score</t>
         </is>
       </c>
       <c r="S1" s="1" t="inlineStr">
@@ -562,7 +520,7 @@
       </c>
       <c r="T1" s="1" t="inlineStr">
         <is>
-          <t>Dim5_Education_Score (0-3)</t>
+          <t>Dim5_Tenure_Score</t>
         </is>
       </c>
       <c r="U1" s="1" t="inlineStr">
@@ -572,42 +530,42 @@
       </c>
       <c r="V1" s="1" t="inlineStr">
         <is>
-          <t>Dim6_RecruitingOps_Score (0-3)</t>
+          <t>Bonus1_US_Co_Score</t>
         </is>
       </c>
       <c r="W1" s="1" t="inlineStr">
         <is>
-          <t>Dim6_Note</t>
+          <t>Bonus1_Note</t>
         </is>
       </c>
       <c r="X1" s="1" t="inlineStr">
         <is>
-          <t>Dim7_Tenure_Score (0-3)</t>
+          <t>Bonus2_Startup_Score</t>
         </is>
       </c>
       <c r="Y1" s="1" t="inlineStr">
         <is>
-          <t>Dim7_Note</t>
+          <t>Bonus2_Note</t>
         </is>
       </c>
       <c r="Z1" s="1" t="inlineStr">
         <is>
-          <t>Bonus1_US_Co_Score (0-3)</t>
+          <t>Bonus3_SalesHiring_Score</t>
         </is>
       </c>
       <c r="AA1" s="1" t="inlineStr">
         <is>
-          <t>Bonus1_Note</t>
+          <t>Bonus3_Note</t>
         </is>
       </c>
       <c r="AB1" s="1" t="inlineStr">
         <is>
-          <t>Bonus2_Startup_Score (0-4)</t>
+          <t>Bonus4_Education_Score</t>
         </is>
       </c>
       <c r="AC1" s="1" t="inlineStr">
         <is>
-          <t>Bonus2_Note</t>
+          <t>Bonus4_Note</t>
         </is>
       </c>
       <c r="AD1" s="1" t="inlineStr">
@@ -617,50 +575,60 @@
       </c>
       <c r="AE1" s="1" t="inlineStr">
         <is>
-          <t>US_Co_Bonus (Bonus1 × 0.8)</t>
+          <t>US_Co_Bonus</t>
         </is>
       </c>
       <c r="AF1" s="1" t="inlineStr">
         <is>
-          <t>Startup_Bonus (Bonus2 × 2)</t>
+          <t>Startup_Bonus</t>
         </is>
       </c>
       <c r="AG1" s="1" t="inlineStr">
         <is>
-          <t>Raw_Score (Base + Bonuses)</t>
+          <t>SalesHiring_Bonus</t>
         </is>
       </c>
       <c r="AH1" s="1" t="inlineStr">
         <is>
+          <t>Education_Bonus</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>Raw_Score</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
           <t>Max_Score</t>
         </is>
       </c>
-      <c r="AI1" s="1" t="inlineStr">
+      <c r="AK1" s="1" t="inlineStr">
         <is>
           <t>Percentage</t>
         </is>
       </c>
-      <c r="AJ1" s="1" t="inlineStr">
+      <c r="AL1" s="1" t="inlineStr">
         <is>
           <t>Tier</t>
         </is>
       </c>
-      <c r="AK1" s="1" t="inlineStr">
+      <c r="AM1" s="1" t="inlineStr">
         <is>
           <t>Verdict</t>
         </is>
       </c>
-      <c r="AL1" s="1" t="inlineStr">
+      <c r="AN1" s="1" t="inlineStr">
         <is>
           <t>Whys</t>
         </is>
       </c>
-      <c r="AM1" s="1" t="inlineStr">
+      <c r="AO1" s="1" t="inlineStr">
         <is>
           <t>Concern</t>
         </is>
       </c>
-      <c r="AN1" s="1" t="inlineStr">
+      <c r="AP1" s="1" t="inlineStr">
         <is>
           <t>Cleaned?</t>
         </is>
